--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487759_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487759_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3304</v>
+        <v>7.3517</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2937</v>
+        <v>5.1976</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0367</v>
+        <v>2.1541</v>
       </c>
       <c r="G2" t="n">
         <v>5.796</v>
@@ -610,13 +610,13 @@
         <v>2.7055</v>
       </c>
       <c r="S2" t="n">
-        <v>0.013</v>
+        <v>1.0344</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1115</v>
+        <v>1.0154</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0984</v>
+        <v>0.019</v>
       </c>
       <c r="V2" t="n">
         <v>0.9376</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8693</v>
+        <v>6.2023</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7621</v>
+        <v>4.5355</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1072</v>
+        <v>1.6668</v>
       </c>
       <c r="G3" t="n">
         <v>3.5039</v>
@@ -688,13 +688,13 @@
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9866</v>
+        <v>2.3196</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2172</v>
+        <v>0.9906</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7694</v>
+        <v>1.329</v>
       </c>
       <c r="V3" t="n">
         <v>1.6275</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7539</v>
+        <v>3.1915</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3691</v>
+        <v>1.071</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3848</v>
+        <v>2.1205</v>
       </c>
       <c r="G4" t="n">
         <v>0.1311</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>2.166</v>
+        <v>1.6036</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4378</v>
+        <v>1.1397</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7282</v>
+        <v>0.4639</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1755</v>
+        <v>2.6189</v>
       </c>
       <c r="E5" t="n">
-        <v>1.652</v>
+        <v>0.9485</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5235</v>
+        <v>1.6703</v>
       </c>
       <c r="G5" t="n">
         <v>2.6647</v>
@@ -844,13 +844,13 @@
         <v>1.8731</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7595</v>
+        <v>1.2029</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0217</v>
+        <v>1.3183</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2622</v>
+        <v>-0.1154</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>J. RODRIGUEZ NERI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1699</v>
+        <v>-0.0847</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1733</v>
+        <v>0.1072</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3433</v>
+        <v>-0.1919</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3304</v>
+        <v>-0.1919</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7804</v>
+        <v>-0.1919</v>
       </c>
       <c r="I6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1925</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7188</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9112</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5228</v>
+        <v>-0.1919</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0616</v>
+        <v>-0.1919</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4613</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.2893</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4498</v>
+        <v>0.1072</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1027</v>
+        <v>0.1072</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3471</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ NERI</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1919</v>
+        <v>-0.7561</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.8921</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1919</v>
+        <v>0.136</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1919</v>
+        <v>-3.5845</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1919</v>
+        <v>-0.5075</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-3.0771</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-2.5433</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.7543</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-3.2976</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1919</v>
+        <v>-1.0413</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1919</v>
+        <v>-1.2617</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.2205</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2893</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.2893</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.6005</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.545</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.0555</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0614</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.725</v>
+        <v>-1.2708</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8316</v>
+        <v>-0.8982</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1067</v>
+        <v>-0.3726</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5845</v>
+        <v>-0.3304</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5075</v>
+        <v>-1.7804</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0771</v>
+        <v>1.45</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5433</v>
+        <v>1.1925</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7543</v>
+        <v>-0.7188</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2976</v>
+        <v>1.9112</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0413</v>
+        <v>-1.5228</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2617</v>
+        <v>-1.0616</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2205</v>
+        <v>-0.4613</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2893</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6317</v>
+        <v>1.3488</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6055</v>
+        <v>1.0311</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0262</v>
+        <v>0.3178</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0614</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1061</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1626</v>
+        <v>-1.4755</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5384</v>
+        <v>-1.0568</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6242</v>
+        <v>-0.4187</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5913</v>
@@ -1156,13 +1156,13 @@
         <v>2.2893</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1769</v>
+        <v>0.5102</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6029</v>
+        <v>0.8787</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.3685</v>
       </c>
       <c r="V9" t="n">
         <v>1.3975</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1918</v>
+        <v>-2.7845</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0862</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1056</v>
+        <v>-1.8707</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3362</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2714</v>
+        <v>0.6787</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5434</v>
+        <v>0.7158</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.272</v>
+        <v>-0.0372</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3351</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>11.6879</v>
+        <v>12.9928</v>
       </c>
       <c r="E11" t="n">
-        <v>6.794000000000002</v>
+        <v>8.0989</v>
       </c>
       <c r="F11" t="n">
-        <v>4.893899999999999</v>
+        <v>4.8938</v>
       </c>
       <c r="G11" t="n">
         <v>3.061400000000001</v>
@@ -1312,13 +1312,13 @@
         <v>14.5683</v>
       </c>
       <c r="S11" t="n">
-        <v>9.101099999999999</v>
+        <v>10.4059</v>
       </c>
       <c r="T11" t="n">
-        <v>7.4369</v>
+        <v>8.7418</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6642</v>
+        <v>1.6641</v>
       </c>
       <c r="V11" t="n">
         <v>0.5661</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.6137</v>
+        <v>5.1534</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4683</v>
+        <v>3.5755</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1454</v>
+        <v>1.5779</v>
       </c>
       <c r="G12" t="n">
         <v>5.1836</v>
@@ -1390,13 +1390,13 @@
         <v>2.2893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.008</v>
+        <v>-0.4683</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0562</v>
+        <v>0.051</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9518</v>
+        <v>-0.5193</v>
       </c>
       <c r="V12" t="n">
         <v>0.23</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1553</v>
+        <v>0.3103</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6165</v>
+        <v>2.3483</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4612</v>
+        <v>-2.038</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0992</v>
+        <v>1.4351</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7337</v>
+        <v>2.3944</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6345</v>
+        <v>-0.9593</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5772</v>
+        <v>2.6436</v>
       </c>
       <c r="K13" t="n">
-        <v>2.183</v>
+        <v>2.6436</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6058</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.478</v>
+        <v>-1.2085</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4494</v>
+        <v>-0.2492</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0287</v>
+        <v>-0.9593</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9137</v>
+        <v>0.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6733</v>
+        <v>-0.5816</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9935</v>
+        <v>-0.2952</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6668</v>
+        <v>-0.2864</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9376</v>
+        <v>-1.1675</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1017</v>
+        <v>0.0497</v>
       </c>
       <c r="E14" t="n">
-        <v>2.134</v>
+        <v>-0.2407</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2357</v>
+        <v>0.2904</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4351</v>
+        <v>0.0992</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3944</v>
+        <v>1.7337</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9593</v>
+        <v>-1.6345</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6436</v>
+        <v>1.5772</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6436</v>
+        <v>2.183</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.6058</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2085</v>
+        <v>-1.478</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2492</v>
+        <v>-0.4494</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9593</v>
+        <v>-1.0287</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6244</v>
+        <v>2.9137</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9936</v>
+        <v>-0.779</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.1363</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.484</v>
+        <v>-0.9153</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1675</v>
+        <v>0.9376</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.1555</v>
+        <v>-1.3301</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4632</v>
+        <v>-1.2133</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6923</v>
+        <v>-0.1168</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5177</v>
@@ -1624,13 +1624,13 @@
         <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5546</v>
+        <v>-0.7292</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7202</v>
+        <v>-0.0299</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2747</v>
+        <v>-0.6993</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7076</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6853</v>
+        <v>-1.6012</v>
       </c>
       <c r="E16" t="n">
         <v>-0.6061</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0793</v>
+        <v>-0.9951</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7577</v>
@@ -1702,13 +1702,13 @@
         <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.884</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3138</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5702</v>
+        <v>-0.486</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4599</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3636</v>
+        <v>-2.0842</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4179</v>
+        <v>-1.3107</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9457</v>
+        <v>-0.7735</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0596</v>
@@ -1780,13 +1780,13 @@
         <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0334</v>
+        <v>-0.754</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5219</v>
+        <v>-0.4148</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5115</v>
+        <v>-0.3392</v>
       </c>
       <c r="V17" t="n">
         <v>0.3538</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2059</v>
+        <v>-2.5217</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1122</v>
+        <v>-2.2994</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0938</v>
+        <v>-0.2223</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5141</v>
+        <v>-3.2406</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0106</v>
+        <v>-3.8211</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4965</v>
+        <v>0.5805</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1963</v>
+        <v>-3.4403</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4517</v>
+        <v>-3.5187</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7446</v>
+        <v>0.0784</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6821</v>
+        <v>0.1998</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4411</v>
+        <v>-0.3023</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2411</v>
+        <v>0.5021</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4901</v>
+        <v>-0.0481</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1866</v>
+        <v>-0.0266</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3035</v>
+        <v>-0.0215</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3975</v>
+        <v>-0.6899</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3975</v>
+        <v>-1.8574</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2258</v>
+        <v>-3.1051</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8352</v>
+        <v>-0.3265</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3906</v>
+        <v>-2.7787</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.2406</v>
+        <v>0.5141</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.8211</v>
+        <v>2.0106</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5805</v>
+        <v>-1.4965</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.4403</v>
+        <v>3.1963</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.5187</v>
+        <v>2.4517</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0784</v>
+        <v>0.7446</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1998</v>
+        <v>-2.6821</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3023</v>
+        <v>-0.4411</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5021</v>
+        <v>-2.2411</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4568</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7522</v>
+        <v>-1.3893</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5624</v>
+        <v>-0.401</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1898</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6899</v>
+        <v>-1.3975</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8574</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.719</v>
+        <v>-3.7013</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.6782</v>
+        <v>-4.821</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9592000000000001</v>
+        <v>1.1197</v>
       </c>
       <c r="G20" t="n">
         <v>-4.7179</v>
@@ -2014,13 +2014,13 @@
         <v>2.4974</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7119</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2272</v>
+        <v>-0.37</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4846</v>
+        <v>-0.3242</v>
       </c>
       <c r="V20" t="n">
         <v>2.3351</v>
@@ -2047,16 +2047,16 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-11.6878</v>
+        <v>-8.830200000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.894</v>
+        <v>-4.893899999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.794</v>
+        <v>-3.936400000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.061500000000001</v>
+        <v>-3.0615</v>
       </c>
       <c r="H21" t="n">
         <v>4.776300000000001</v>
@@ -2065,7 +2065,7 @@
         <v>-7.8377</v>
       </c>
       <c r="J21" t="n">
-        <v>7.1461</v>
+        <v>7.146100000000001</v>
       </c>
       <c r="K21" t="n">
         <v>8.2483</v>
@@ -2092,13 +2092,13 @@
         <v>15.6088</v>
       </c>
       <c r="S21" t="n">
-        <v>-9.101100000000001</v>
+        <v>-6.2435</v>
       </c>
       <c r="T21" t="n">
         <v>-1.664</v>
       </c>
       <c r="U21" t="n">
-        <v>-7.436900000000001</v>
+        <v>-4.5796</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5658999999999996</v>
